--- a/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
+++ b/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:11:33+00:00</t>
+    <t>2026-06-16T11:48:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
+++ b/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:48:44+00:00</t>
+    <t>2026-06-16T12:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
+++ b/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:08:45+00:00</t>
+    <t>2026-06-16T12:20:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
+++ b/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:20:50+00:00</t>
+    <t>2026-06-16T12:25:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
+++ b/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:01+00:00</t>
+    <t>2026-06-16T12:31:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
+++ b/preview/pr-4/ValueSet-dem-geschlecht-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:31:51+00:00</t>
+    <t>2026-06-16T12:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
